--- a/assets/scene_presets.xlsx
+++ b/assets/scene_presets.xlsx
@@ -1,34 +1,99 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C7B0CB0-EB35-400A-8D43-C0A3BC50C077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Presets" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Presets" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>tooltip</t>
+  </si>
+  <si>
+    <t>cam_x</t>
+  </si>
+  <si>
+    <t>cam_y</t>
+  </si>
+  <si>
+    <t>cam_z</t>
+  </si>
+  <si>
+    <t>tgt_x</t>
+  </si>
+  <si>
+    <t>tgt_y</t>
+  </si>
+  <si>
+    <t>tgt_z</t>
+  </si>
+  <si>
+    <t>floor_index</t>
+  </si>
+  <si>
+    <t>layers</t>
+  </si>
+  <si>
+    <t>flow_paused</t>
+  </si>
+  <si>
+    <t>labels_hidden</t>
+  </si>
+  <si>
+    <t>loc_name:0,zones_noname:0,zones:1,zones_building:0,clock:0,it_dev:0,prod_comp:0,weight:0,machine:0,inspect:0,form_can_1:0,form_can_2:0,form_pouch_1:0,form_pouch_2:0,flow_powder:1,flow_pouch:1,flow_can:1,flow_rtd:0</t>
+  </si>
+  <si>
+    <t>Powder</t>
+  </si>
+  <si>
+    <t>Powder Production, 1st Floor</t>
+  </si>
+  <si>
+    <t>Powder Production, 2nd Floor</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +112,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,79 +414,144 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="2.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="193.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>tooltip</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>cam_x</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>cam_y</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>cam_z</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>tgt_x</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>tgt_y</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>tgt_z</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>floor_index</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>layers</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>flow_paused</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>labels_hidden</t>
-        </is>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2">
+        <v>-1086</v>
+      </c>
+      <c r="E2">
+        <v>1567</v>
+      </c>
+      <c r="F2">
+        <v>1046</v>
+      </c>
+      <c r="G2">
+        <v>-150</v>
+      </c>
+      <c r="H2">
+        <v>366</v>
+      </c>
+      <c r="I2">
+        <v>-360</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3">
+        <v>361</v>
+      </c>
+      <c r="E3">
+        <v>1101</v>
+      </c>
+      <c r="F3">
+        <v>424</v>
+      </c>
+      <c r="G3">
+        <v>689</v>
+      </c>
+      <c r="H3">
+        <v>680</v>
+      </c>
+      <c r="I3">
+        <v>-69</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/assets/scene_presets.xlsx
+++ b/assets/scene_presets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M.Mead\9.FactoryView\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C7B0CB0-EB35-400A-8D43-C0A3BC50C077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABF9B75-6632-4FB1-BC9C-608FC06AE974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presets" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
   <si>
     <t>id</t>
   </si>
@@ -66,16 +66,133 @@
     <t>labels_hidden</t>
   </si>
   <si>
-    <t>loc_name:0,zones_noname:0,zones:1,zones_building:0,clock:0,it_dev:0,prod_comp:0,weight:0,machine:0,inspect:0,form_can_1:0,form_can_2:0,form_pouch_1:0,form_pouch_2:0,flow_powder:1,flow_pouch:1,flow_can:1,flow_rtd:0</t>
-  </si>
-  <si>
-    <t>Powder</t>
-  </si>
-  <si>
-    <t>Powder Production, 1st Floor</t>
-  </si>
-  <si>
-    <t>Powder Production, 2nd Floor</t>
+    <t>loc_name:0,zones_noname:0,zones:1,building:0,clock:0,it_dev:0,prod_comp:0,weight:0,machine:0,inspect:0,form_can_1:0,form_can_2:0,form_pouch_1:0,form_pouch_2:0,flow_powder:1,flow_pouch:1,flow_can:1,flow_rtd:0</t>
+  </si>
+  <si>
+    <t>loc_name:0,zones_noname:0,zones:0,building:1,clock:0,it_dev:0,prod_comp:0,weight:0,machine:0,inspect:0,form_can_1:0,form_can_2:0,form_pouch_1:0,form_pouch_2:0,flow_powder:0,flow_pouch:0,flow_can:0,flow_rtd:0</t>
+  </si>
+  <si>
+    <t>Building</t>
+  </si>
+  <si>
+    <t>Overall Building</t>
+  </si>
+  <si>
+    <t>loc_name:0,zones_noname:0,zones:1,building:0,clock:0,it_dev:0,prod_comp:0,weight:0,machine:0,inspect:0,form_can_1:0,form_can_2:0,form_pouch_1:0,form_pouch_2:0,flow_powder:0,flow_pouch:0,flow_can:0,flow_rtd:0</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Floor Top View</t>
+  </si>
+  <si>
+    <t>loc_name:0,zones_noname:0,zones:1,building:0,clock:0,it_dev:0,prod_comp:0,weight:0,machine:1,inspect:0,form_can_1:0,form_can_2:0,form_pouch_1:0,form_pouch_2:0,flow_powder:1,flow_pouch:1,flow_can:0,flow_rtd:0</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>loc_name:0,zones_noname:0,zones:1,building:0,clock:0,it_dev:0,prod_comp:0,weight:0,machine:0,inspect:1,form_can_1:0,form_can_2:0,form_pouch_1:0,form_pouch_2:0,flow_powder:1,flow_pouch:1,flow_can:0,flow_rtd:0</t>
+  </si>
+  <si>
+    <t>Ins</t>
+  </si>
+  <si>
+    <t>Inspection Device</t>
+  </si>
+  <si>
+    <t>Machine</t>
+  </si>
+  <si>
+    <t>loc_name:0,zones_noname:0,zones:1,building:0,clock:0,it_dev:0,prod_comp:1,weight:0,machine:0,inspect:0,form_can_1:0,form_can_2:0,form_pouch_1:0,form_pouch_2:0,flow_powder:1,flow_pouch:0,flow_can:0,flow_rtd:0</t>
+  </si>
+  <si>
+    <t>PCS1</t>
+  </si>
+  <si>
+    <t>loc_name:0,zones_noname:0,zones:1,building:0,clock:0,it_dev:0,prod_comp:1,weight:1,machine:0,inspect:0,form_can_1:0,form_can_2:0,form_pouch_1:0,form_pouch_2:0,flow_powder:1,flow_pouch:0,flow_can:0,flow_rtd:0</t>
+  </si>
+  <si>
+    <t>PCS2</t>
+  </si>
+  <si>
+    <t>Powder Production, Floor 1</t>
+  </si>
+  <si>
+    <t>Powder Production, Floor 2</t>
+  </si>
+  <si>
+    <t>GWINS, Scan&amp;Tips, Floor 1</t>
+  </si>
+  <si>
+    <t>GWINS, Scan&amp;Tips, Floor 2</t>
+  </si>
+  <si>
+    <t>Form at Pouch, 1st half</t>
+  </si>
+  <si>
+    <t>loc_name:0,zones_noname:0,zones:1,building:0,clock:0,it_dev:0,prod_comp:0,weight:0,machine:0,inspect:0,form_can_1:0,form_can_2:0,form_pouch_1:1,form_pouch_2:0,flow_powder:1,flow_pouch:0,flow_can:0,flow_rtd:0</t>
+  </si>
+  <si>
+    <t>loc_name:0,zones_noname:0,zones:1,building:0,clock:0,it_dev:0,prod_comp:0,weight:0,machine:0,inspect:0,form_can_1:0,form_can_2:0,form_pouch_1:0,form_pouch_2:1,flow_powder:0,flow_pouch:1,flow_can:0,flow_rtd:0</t>
+  </si>
+  <si>
+    <t>Form at Pouch, 2nd half, 1</t>
+  </si>
+  <si>
+    <t>Form at Pouch, 2nd half, 2</t>
+  </si>
+  <si>
+    <t>Fc1</t>
+  </si>
+  <si>
+    <t>Form at Can, 1st half</t>
+  </si>
+  <si>
+    <t>Fp1</t>
+  </si>
+  <si>
+    <t>Fp2.1</t>
+  </si>
+  <si>
+    <t>Fp2.2</t>
+  </si>
+  <si>
+    <t>loc_name:0,zones_noname:0,zones:1,building:0,clock:0,it_dev:0,prod_comp:0,weight:0,machine:0,inspect:0,form_can_1:1,form_can_2:0,form_pouch_1:0,form_pouch_2:0,flow_powder:1,flow_pouch:0,flow_can:0,flow_rtd:0</t>
+  </si>
+  <si>
+    <t>loc_name:0,zones_noname:0,zones:1,building:0,clock:0,it_dev:0,prod_comp:0,weight:0,machine:0,inspect:0,form_can_1:0,form_can_2:1,form_pouch_1:0,form_pouch_2:0,flow_powder:0,flow_pouch:0,flow_can:1,flow_rtd:0</t>
+  </si>
+  <si>
+    <t>Fc2</t>
+  </si>
+  <si>
+    <t>Form at Can, 2nd half</t>
+  </si>
+  <si>
+    <t>loc_name:0,zones_noname:0,zones:1,building:0,clock:0,it_dev:0,prod_comp:0,weight:0,machine:0,inspect:0,form_can_1:0,form_can_2:1,form_pouch_1:1,form_pouch_2:1,flow_powder:1,flow_pouch:1,flow_can:1,flow_rtd:0</t>
+  </si>
+  <si>
+    <t>F-all</t>
+  </si>
+  <si>
+    <t>All Forms</t>
+  </si>
+  <si>
+    <t>loc_name:0,zones_noname:0,zones:0,building:1,clock:0,it_dev:0,prod_comp:1,weight:0,machine:0,inspect:0,form_can_1:0,form_can_2:0,form_pouch_1:0,form_pouch_2:0,flow_powder:0,flow_pouch:0,flow_can:0,flow_rtd:1</t>
+  </si>
+  <si>
+    <t>RTD</t>
+  </si>
+  <si>
+    <t>Basic RTD</t>
   </si>
 </sst>
 </file>
@@ -415,12 +532,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="6.375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.25" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="5.125" bestFit="1" customWidth="1"/>
@@ -477,34 +594,34 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2">
+        <v>2528</v>
+      </c>
+      <c r="E2">
+        <v>2402</v>
+      </c>
+      <c r="F2">
+        <v>2999</v>
+      </c>
+      <c r="G2">
+        <v>113</v>
+      </c>
+      <c r="H2">
+        <v>55</v>
+      </c>
+      <c r="I2">
+        <v>-540</v>
+      </c>
+      <c r="J2">
+        <v>-1</v>
+      </c>
+      <c r="K2" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2">
-        <v>-1086</v>
-      </c>
-      <c r="E2">
-        <v>1567</v>
-      </c>
-      <c r="F2">
-        <v>1046</v>
-      </c>
-      <c r="G2">
-        <v>-150</v>
-      </c>
-      <c r="H2">
-        <v>366</v>
-      </c>
-      <c r="I2">
-        <v>-360</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
-        <v>13</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -518,39 +635,572 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3">
+        <v>-3</v>
+      </c>
+      <c r="E3">
+        <v>3752</v>
+      </c>
+      <c r="F3">
+        <v>-64</v>
+      </c>
+      <c r="G3">
+        <v>-3</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>-68</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4">
+        <v>-1086</v>
+      </c>
+      <c r="E4">
+        <v>1567</v>
+      </c>
+      <c r="F4">
+        <v>1046</v>
+      </c>
+      <c r="G4">
+        <v>-150</v>
+      </c>
+      <c r="H4">
+        <v>366</v>
+      </c>
+      <c r="I4">
+        <v>-360</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5">
+        <v>361</v>
+      </c>
+      <c r="E5">
+        <v>1101</v>
+      </c>
+      <c r="F5">
+        <v>424</v>
+      </c>
+      <c r="G5">
+        <v>689</v>
+      </c>
+      <c r="H5">
+        <v>680</v>
+      </c>
+      <c r="I5">
+        <v>-69</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6">
+        <v>-51</v>
+      </c>
+      <c r="E6">
+        <v>1267</v>
+      </c>
+      <c r="F6">
+        <v>827</v>
+      </c>
+      <c r="G6">
+        <v>454</v>
+      </c>
+      <c r="H6">
+        <v>451</v>
+      </c>
+      <c r="I6">
+        <v>-30</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>-51</v>
+      </c>
+      <c r="E7">
+        <v>1267</v>
+      </c>
+      <c r="F7">
+        <v>827</v>
+      </c>
+      <c r="G7">
+        <v>454</v>
+      </c>
+      <c r="H7">
+        <v>451</v>
+      </c>
+      <c r="I7">
+        <v>-30</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8">
+        <v>463</v>
+      </c>
+      <c r="E8">
+        <v>675</v>
+      </c>
+      <c r="F8">
+        <v>93</v>
+      </c>
+      <c r="G8">
+        <v>529</v>
+      </c>
+      <c r="H8">
+        <v>535</v>
+      </c>
+      <c r="I8">
+        <v>-49</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9">
+        <v>609</v>
+      </c>
+      <c r="E9">
+        <v>914</v>
+      </c>
+      <c r="F9">
+        <v>-75</v>
+      </c>
+      <c r="G9">
+        <v>676</v>
+      </c>
+      <c r="H9">
+        <v>774</v>
+      </c>
+      <c r="I9">
+        <v>-217</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>30</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10">
+        <v>650</v>
+      </c>
+      <c r="E10">
+        <v>1095</v>
+      </c>
+      <c r="F10">
+        <v>-525</v>
+      </c>
+      <c r="G10">
+        <v>650</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>-526</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11">
+        <v>1313</v>
+      </c>
+      <c r="E11">
+        <v>1325</v>
+      </c>
+      <c r="F11">
+        <v>-287</v>
+      </c>
+      <c r="G11">
+        <v>1313</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>-288</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>38</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12">
+        <v>-411</v>
+      </c>
+      <c r="E12">
+        <v>1326</v>
+      </c>
+      <c r="F12">
+        <v>-1123</v>
+      </c>
+      <c r="G12">
+        <v>-411</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>-1124</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" t="s">
+        <v>38</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13">
+        <v>828</v>
+      </c>
+      <c r="E13">
+        <v>1095</v>
+      </c>
+      <c r="F13">
+        <v>-529</v>
+      </c>
+      <c r="G13">
+        <v>828</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>-530</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
+        <v>46</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14">
+        <v>712</v>
+      </c>
+      <c r="E14">
+        <v>1457</v>
+      </c>
+      <c r="F14">
+        <v>-281</v>
+      </c>
+      <c r="G14">
+        <v>712</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>-282</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>47</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3">
-        <v>361</v>
-      </c>
-      <c r="E3">
-        <v>1101</v>
-      </c>
-      <c r="F3">
-        <v>424</v>
-      </c>
-      <c r="G3">
-        <v>689</v>
-      </c>
-      <c r="H3">
-        <v>680</v>
-      </c>
-      <c r="I3">
-        <v>-69</v>
-      </c>
-      <c r="J3">
+      <c r="B15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15">
+        <v>719</v>
+      </c>
+      <c r="E15">
+        <v>1939</v>
+      </c>
+      <c r="F15">
+        <v>-654</v>
+      </c>
+      <c r="G15">
+        <v>719</v>
+      </c>
+      <c r="H15">
         <v>1</v>
       </c>
-      <c r="K3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
+      <c r="I15">
+        <v>-656</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>50</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16">
+        <v>-2067</v>
+      </c>
+      <c r="E16">
+        <v>870</v>
+      </c>
+      <c r="F16">
+        <v>2445</v>
+      </c>
+      <c r="G16">
+        <v>-1965</v>
+      </c>
+      <c r="H16">
+        <v>-118</v>
+      </c>
+      <c r="I16">
+        <v>-1089</v>
+      </c>
+      <c r="J16">
+        <v>-1</v>
+      </c>
+      <c r="K16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
         <v>0</v>
       </c>
     </row>
